--- a/tasks/finalpool/howtocook-nutrition-excel-email/groundtruth_workspace/Breakfast_Nutrition_Report.xlsx
+++ b/tasks/finalpool/howtocook-nutrition-excel-email/groundtruth_workspace/Breakfast_Nutrition_Report.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,16 +442,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Fried Eggs</t>
+          <t>吐司果酱的做法</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>breakfast</t>
+          <t>早餐</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -462,16 +462,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Congee</t>
+          <t>太阳蛋的做法</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>breakfast</t>
+          <t>早餐</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -482,16 +482,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pancakes</t>
+          <t>完美水煮蛋的做法</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>breakfast</t>
+          <t>早餐</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -502,38 +502,378 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>French Toast</t>
+          <t>微波炉荷包蛋的做法</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>breakfast</t>
+          <t>早餐</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>easy</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Steamed Buns</t>
+          <t>微波炉蛋糕的做法</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>breakfast</t>
+          <t>早餐</t>
         </is>
       </c>
       <c r="C6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>手抓饼的做法</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>早餐</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>20</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>桂圆红枣粥的做法</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>早餐</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>水煮玉米的做法</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>早餐</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>9</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>溏心蛋的做法</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>早餐</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>煎饺的做法</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>早餐</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>燕麦鸡蛋饼的做法</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>早餐</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>8</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>牛奶燕麦的做法</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>早餐</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>空气炸锅面包片的做法</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>早餐</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>美式炒蛋的做法</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>早餐</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>茶叶蛋的做法</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>早餐</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>蒸水蛋的做法</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>早餐</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>蒸花卷的做法</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>早餐</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>蛋煎糍粑的做法</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>早餐</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>8</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>金枪鱼酱三明治的做法</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>早餐</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>11</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>鸡蛋三明治的做法</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>早餐</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>14</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>温泉蛋的做法</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>早餐</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>苏格兰蛋的做法</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>早餐</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>9</v>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
@@ -572,7 +912,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -582,7 +922,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.2</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4">
@@ -593,7 +933,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fried Eggs</t>
+          <t>温泉蛋的做法</t>
         </is>
       </c>
     </row>
